--- a/data/trans_orig/P3A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>159562</t>
+          <t>156801</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205405</t>
+          <t>206413</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>557792</t>
+          <t>555359</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>593528</t>
+          <t>593353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>719877</t>
+          <t>719230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>794745</t>
+          <t>793101</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>488607</t>
+          <t>487599</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>534450</t>
+          <t>537211</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93670</t>
+          <t>93845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129406</t>
+          <t>131839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>586465</t>
+          <t>588109</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>661333</t>
+          <t>661980</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>274151</t>
+          <t>271654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>331391</t>
+          <t>332508</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>809255</t>
+          <t>810546</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>853356</t>
+          <t>854216</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1087653</t>
+          <t>1090750</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1177330</t>
+          <t>1181813</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>630409</t>
+          <t>629292</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>687649</t>
+          <t>690146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115037</t>
+          <t>114177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159138</t>
+          <t>157847</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>752863</t>
+          <t>748380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>842540</t>
+          <t>839443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>240347</t>
+          <t>240764</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>294214</t>
+          <t>294711</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>574260</t>
+          <t>574226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>608705</t>
+          <t>608597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>825758</t>
+          <t>825543</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>894213</t>
+          <t>896336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>384295</t>
+          <t>383798</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>438162</t>
+          <t>437745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71738</t>
+          <t>71846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106183</t>
+          <t>106217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>464739</t>
+          <t>462616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>533194</t>
+          <t>533409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>339886</t>
+          <t>340271</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>401000</t>
+          <t>401739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>809938</t>
+          <t>810529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>860648</t>
+          <t>861895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1163456</t>
+          <t>1159868</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1248456</t>
+          <t>1245296</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>540340</t>
+          <t>539601</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>601454</t>
+          <t>601069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177964</t>
+          <t>176717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>228674</t>
+          <t>228083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>731496</t>
+          <t>734656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>816496</t>
+          <t>820084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1063343</t>
+          <t>1064943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1174164</t>
+          <t>1177799</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2789690</t>
+          <t>2791090</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2877311</t>
+          <t>2877241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3881039</t>
+          <t>3878149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4032335</t>
+          <t>4043597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2101497</t>
+          <t>2097862</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2212318</t>
+          <t>2210718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>497334</t>
+          <t>497404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>584955</t>
+          <t>583555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2617972</t>
+          <t>2606710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2769268</t>
+          <t>2772158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>255391</t>
+          <t>251067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>309645</t>
+          <t>304636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>568583</t>
+          <t>568035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>606619</t>
+          <t>604303</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>830225</t>
+          <t>827546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>904892</t>
+          <t>905328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393824</t>
+          <t>398833</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448078</t>
+          <t>452402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90431</t>
+          <t>92747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128467</t>
+          <t>129015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>495627</t>
+          <t>495191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>570294</t>
+          <t>572973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>397512</t>
+          <t>396123</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>460674</t>
+          <t>461838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>824549</t>
+          <t>825744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>875571</t>
+          <t>877635</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1232465</t>
+          <t>1239062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1324111</t>
+          <t>1326955</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,76%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>556214</t>
+          <t>555050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>619376</t>
+          <t>620765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>156613</t>
+          <t>154549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>207635</t>
+          <t>206440</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>724961</t>
+          <t>722117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>816607</t>
+          <t>810010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>299988</t>
+          <t>300437</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>354932</t>
+          <t>361473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>639041</t>
+          <t>639511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>680240</t>
+          <t>681857</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>952098</t>
+          <t>948692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1031071</t>
+          <t>1027058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>402691</t>
+          <t>396150</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457635</t>
+          <t>457186</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94933</t>
+          <t>93316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136132</t>
+          <t>135662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>501725</t>
+          <t>505738</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>580698</t>
+          <t>584104</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>427169</t>
+          <t>425181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>490022</t>
+          <t>490351</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>846457</t>
+          <t>844167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>895389</t>
+          <t>891483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1281629</t>
+          <t>1285571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1371712</t>
+          <t>1370868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>457717</t>
+          <t>457388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>520570</t>
+          <t>522558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156512</t>
+          <t>160418</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205444</t>
+          <t>207734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>627928</t>
+          <t>628772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>718011</t>
+          <t>714069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1433624</t>
+          <t>1437310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1559438</t>
+          <t>1559799</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2921499</t>
+          <t>2926098</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3015622</t>
+          <t>3019903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4384190</t>
+          <t>4386140</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4552911</t>
+          <t>4552176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1866281</t>
+          <t>1865920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1992095</t>
+          <t>1988409</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>540686</t>
+          <t>536405</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>634809</t>
+          <t>630210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2429116</t>
+          <t>2429851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2597837</t>
+          <t>2595887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>296081</t>
+          <t>296666</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>348981</t>
+          <t>347631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>566587</t>
+          <t>564985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>602557</t>
+          <t>599797</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>870217</t>
+          <t>871669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>940617</t>
+          <t>940327</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>325819</t>
+          <t>327169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>378719</t>
+          <t>378134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69348</t>
+          <t>72108</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105318</t>
+          <t>106920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>406088</t>
+          <t>406378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>476488</t>
+          <t>475036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>493974</t>
+          <t>492302</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>559046</t>
+          <t>556237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>907355</t>
+          <t>906187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>947626</t>
+          <t>949307</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1410822</t>
+          <t>1410036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1494811</t>
+          <t>1496392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,52%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462412</t>
+          <t>465221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>527484</t>
+          <t>529156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94333</t>
+          <t>92652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134604</t>
+          <t>135772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568606</t>
+          <t>567025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>652595</t>
+          <t>653381</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>366825</t>
+          <t>365176</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>424149</t>
+          <t>422987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>672359</t>
+          <t>671908</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>707189</t>
+          <t>708477</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1047969</t>
+          <t>1050873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1123393</t>
+          <t>1123556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,02%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>331540</t>
+          <t>332702</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>388864</t>
+          <t>390513</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75790</t>
+          <t>74502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110620</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>415275</t>
+          <t>415112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>490699</t>
+          <t>487795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>524891</t>
+          <t>523024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>585634</t>
+          <t>585952</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>862425</t>
+          <t>864994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>912290</t>
+          <t>912160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1405067</t>
+          <t>1406466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1485272</t>
+          <t>1486032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347728</t>
+          <t>347410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>408471</t>
+          <t>410338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130448</t>
+          <t>130578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180313</t>
+          <t>177744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>490828</t>
+          <t>490068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>571033</t>
+          <t>569634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1739920</t>
+          <t>1734100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1853938</t>
+          <t>1856067</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3055840</t>
+          <t>3051482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3134887</t>
+          <t>3135285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4810233</t>
+          <t>4816483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4968766</t>
+          <t>4963963</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1531371</t>
+          <t>1529242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1645389</t>
+          <t>1651209</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>404693</t>
+          <t>404295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>483740</t>
+          <t>488098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1956124</t>
+          <t>1960927</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2114657</t>
+          <t>2108407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>372385</t>
+          <t>371840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>427817</t>
+          <t>428157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>667438</t>
+          <t>666884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>692558</t>
+          <t>692062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1043579</t>
+          <t>1043492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1121855</t>
+          <t>1118120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>207158</t>
+          <t>206818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262590</t>
+          <t>263135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32772</t>
+          <t>33268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57892</t>
+          <t>58446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>238450</t>
+          <t>242185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>316726</t>
+          <t>316813</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>333978</t>
+          <t>296623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>793333</t>
+          <t>791176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>864063</t>
+          <t>865503</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>898875</t>
+          <t>898428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1023615</t>
+          <t>1017286</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1708519</t>
+          <t>1708633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399531</t>
+          <t>401688</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>858886</t>
+          <t>896241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59776</t>
+          <t>60223</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94588</t>
+          <t>93148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442997</t>
+          <t>442883</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1127901</t>
+          <t>1134230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>448385</t>
+          <t>447112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>507459</t>
+          <t>507257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>839449</t>
+          <t>842797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>899971</t>
+          <t>904586</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1291978</t>
+          <t>1289041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1447117</t>
+          <t>1445410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,24%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>197221</t>
+          <t>197423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>256295</t>
+          <t>257568</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33395</t>
+          <t>28780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93917</t>
+          <t>90569</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190929</t>
+          <t>192636</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>346068</t>
+          <t>349005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>590454</t>
+          <t>588974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>653645</t>
+          <t>652798</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>938175</t>
+          <t>935813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>993110</t>
+          <t>990670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1540611</t>
+          <t>1542309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1642909</t>
+          <t>1643001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>272554</t>
+          <t>273401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>335745</t>
+          <t>337225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100563</t>
+          <t>103003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155498</t>
+          <t>157860</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376962</t>
+          <t>376870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>479260</t>
+          <t>477562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1645467</t>
+          <t>1616269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2299797</t>
+          <t>2302431</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3352739</t>
+          <t>3353826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3457073</t>
+          <t>3455773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4804174</t>
+          <t>4883769</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5760368</t>
+          <t>5758566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1158921</t>
+          <t>1156287</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1813251</t>
+          <t>1842449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>253947</t>
+          <t>255247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>358281</t>
+          <t>357194</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1409370</t>
+          <t>1411172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2365564</t>
+          <t>2285969</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156801</t>
+          <t>159613</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>206413</t>
+          <t>204099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>555359</t>
+          <t>557099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>593353</t>
+          <t>593219</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>719230</t>
+          <t>722857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>793101</t>
+          <t>794488</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>487599</t>
+          <t>489913</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>537211</t>
+          <t>534399</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93845</t>
+          <t>93979</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131839</t>
+          <t>130099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>588109</t>
+          <t>586722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>661980</t>
+          <t>658353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>271654</t>
+          <t>274582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>332508</t>
+          <t>334785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>810546</t>
+          <t>809656</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>854216</t>
+          <t>853375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1090750</t>
+          <t>1093021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1181813</t>
+          <t>1186617</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>629292</t>
+          <t>627015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>690146</t>
+          <t>687218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114177</t>
+          <t>115018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>157847</t>
+          <t>158737</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>748380</t>
+          <t>743576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>839443</t>
+          <t>837172</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>240764</t>
+          <t>241422</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>294711</t>
+          <t>294727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>574226</t>
+          <t>573706</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>608597</t>
+          <t>607827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>825543</t>
+          <t>824855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>896336</t>
+          <t>896081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383798</t>
+          <t>383782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>437745</t>
+          <t>437087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71846</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106217</t>
+          <t>106737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>462616</t>
+          <t>462871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>533409</t>
+          <t>534097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>340271</t>
+          <t>341385</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>401739</t>
+          <t>398890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>810529</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>861895</t>
+          <t>859809</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1159868</t>
+          <t>1163397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1245296</t>
+          <t>1247229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>539601</t>
+          <t>542450</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>601069</t>
+          <t>599955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176717</t>
+          <t>178803</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>228083</t>
+          <t>228745</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>734656</t>
+          <t>732723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>820084</t>
+          <t>816555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1064943</t>
+          <t>1064692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1177799</t>
+          <t>1178098</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2791090</t>
+          <t>2796494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2877241</t>
+          <t>2881418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3878149</t>
+          <t>3879112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4043597</t>
+          <t>4037308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2097862</t>
+          <t>2097563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2210718</t>
+          <t>2210969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>497404</t>
+          <t>493227</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>583555</t>
+          <t>578151</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2606710</t>
+          <t>2612999</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2772158</t>
+          <t>2771195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>251067</t>
+          <t>252441</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>304636</t>
+          <t>305688</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>568035</t>
+          <t>566985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>604303</t>
+          <t>605136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>827546</t>
+          <t>832937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>905328</t>
+          <t>905471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,65%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>398833</t>
+          <t>397781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452402</t>
+          <t>451028</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92747</t>
+          <t>91914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129015</t>
+          <t>130065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>495191</t>
+          <t>495048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>572973</t>
+          <t>567582</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>396123</t>
+          <t>398929</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>461838</t>
+          <t>465165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>825744</t>
+          <t>825366</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>877635</t>
+          <t>877506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1239062</t>
+          <t>1239136</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1326955</t>
+          <t>1330499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,93%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>555050</t>
+          <t>551723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>620765</t>
+          <t>617959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>154549</t>
+          <t>154678</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>206440</t>
+          <t>206818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>722117</t>
+          <t>718573</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810010</t>
+          <t>809936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>300437</t>
+          <t>300768</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>361473</t>
+          <t>357683</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>639511</t>
+          <t>637160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>681857</t>
+          <t>680831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>948692</t>
+          <t>947331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1027058</t>
+          <t>1028937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,13%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>396150</t>
+          <t>399940</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457186</t>
+          <t>456855</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93316</t>
+          <t>94342</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135662</t>
+          <t>138013</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>505738</t>
+          <t>503859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>584104</t>
+          <t>585465</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>425181</t>
+          <t>426500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>490351</t>
+          <t>494160</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>844167</t>
+          <t>845185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>891483</t>
+          <t>895962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1285571</t>
+          <t>1283575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1370868</t>
+          <t>1370558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,54%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>457388</t>
+          <t>453579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>522558</t>
+          <t>521239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160418</t>
+          <t>155939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207734</t>
+          <t>206716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>628772</t>
+          <t>629082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>714069</t>
+          <t>716065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1437310</t>
+          <t>1437562</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1559799</t>
+          <t>1557613</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2926098</t>
+          <t>2923419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3019903</t>
+          <t>3017987</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4386140</t>
+          <t>4385240</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4552176</t>
+          <t>4552131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1865920</t>
+          <t>1868106</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1988409</t>
+          <t>1988157</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>536405</t>
+          <t>538321</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>630210</t>
+          <t>632889</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2429851</t>
+          <t>2429896</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2595887</t>
+          <t>2596787</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>296666</t>
+          <t>298031</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>347631</t>
+          <t>348530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>564985</t>
+          <t>566662</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>599797</t>
+          <t>601249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>871669</t>
+          <t>876044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>940327</t>
+          <t>945033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>327169</t>
+          <t>326270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>378134</t>
+          <t>376769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72108</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106920</t>
+          <t>105243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>406378</t>
+          <t>401672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>475036</t>
+          <t>470661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>492302</t>
+          <t>487496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>556237</t>
+          <t>554290</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>906187</t>
+          <t>905842</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>949307</t>
+          <t>949390</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1410036</t>
+          <t>1406975</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1496392</t>
+          <t>1494837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465221</t>
+          <t>467168</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>529156</t>
+          <t>533962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92652</t>
+          <t>92569</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135772</t>
+          <t>136117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>567025</t>
+          <t>568580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>653381</t>
+          <t>656442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>365176</t>
+          <t>359957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>422987</t>
+          <t>420043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>671908</t>
+          <t>672528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>708477</t>
+          <t>708543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1050873</t>
+          <t>1048210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1123556</t>
+          <t>1120240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>332702</t>
+          <t>335646</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>390513</t>
+          <t>395732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74502</t>
+          <t>74436</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>110451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>415112</t>
+          <t>418428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>487795</t>
+          <t>490458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>523024</t>
+          <t>527404</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>585952</t>
+          <t>589717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>864994</t>
+          <t>861429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>912160</t>
+          <t>911542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1406466</t>
+          <t>1407470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1486032</t>
+          <t>1482975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347410</t>
+          <t>343645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>410338</t>
+          <t>405958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130578</t>
+          <t>131196</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177744</t>
+          <t>181309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>490068</t>
+          <t>493125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569634</t>
+          <t>568630</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1734100</t>
+          <t>1732899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1856067</t>
+          <t>1853887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3051482</t>
+          <t>3055023</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3135285</t>
+          <t>3134357</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4816483</t>
+          <t>4818389</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4963963</t>
+          <t>4971138</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1529242</t>
+          <t>1531422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1651209</t>
+          <t>1652410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>404295</t>
+          <t>405223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>488098</t>
+          <t>484557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1960927</t>
+          <t>1953752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2108407</t>
+          <t>2106501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>401782</t>
+          <t>432141</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371840</t>
+          <t>404275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>428157</t>
+          <t>458547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>680879</t>
+          <t>685471</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>666884</t>
+          <t>669777</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>692062</t>
+          <t>695963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1082661</t>
+          <t>1117612</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1043492</t>
+          <t>1078691</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1118120</t>
+          <t>1148761</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>233193</t>
+          <t>258085</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>206818</t>
+          <t>231679</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263135</t>
+          <t>285951</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44451</t>
+          <t>48709</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33268</t>
+          <t>38217</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58446</t>
+          <t>64403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>277644</t>
+          <t>306794</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>242185</t>
+          <t>275645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>316813</t>
+          <t>345715</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634975</t>
+          <t>690226</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634975</t>
+          <t>690226</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634975</t>
+          <t>690226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360305</t>
+          <t>1424406</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360305</t>
+          <t>1424406</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360305</t>
+          <t>1424406</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>619109</t>
+          <t>681901</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>296623</t>
+          <t>644439</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>791176</t>
+          <t>716147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>883438</t>
+          <t>985056</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>865503</t>
+          <t>963321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>898428</t>
+          <t>1002231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1502548</t>
+          <t>1666957</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1017286</t>
+          <t>1624680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1708633</t>
+          <t>1706175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>573755</t>
+          <t>367016</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401688</t>
+          <t>332770</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>896241</t>
+          <t>404478</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>75213</t>
+          <t>86418</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60223</t>
+          <t>69243</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93148</t>
+          <t>108153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>648968</t>
+          <t>453434</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442883</t>
+          <t>414216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1134230</t>
+          <t>495711</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>477663</t>
+          <t>542863</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>447112</t>
+          <t>511170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>507257</t>
+          <t>572086</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>870118</t>
+          <t>736714</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>842797</t>
+          <t>714114</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>904586</t>
+          <t>754309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1347781</t>
+          <t>1279576</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1289041</t>
+          <t>1235786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1445410</t>
+          <t>1317392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>227017</t>
+          <t>260210</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>197423</t>
+          <t>230987</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257568</t>
+          <t>291903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63248</t>
+          <t>75545</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28780</t>
+          <t>57950</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90569</t>
+          <t>98145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>290265</t>
+          <t>335756</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>192636</t>
+          <t>297940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>349005</t>
+          <t>379546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>622054</t>
+          <t>655652</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>588974</t>
+          <t>622570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>652798</t>
+          <t>685474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>963142</t>
+          <t>978683</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>935813</t>
+          <t>955018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>990670</t>
+          <t>1001245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1585195</t>
+          <t>1634336</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1542309</t>
+          <t>1591504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1643001</t>
+          <t>1671898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>304145</t>
+          <t>333800</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>273401</t>
+          <t>303978</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337225</t>
+          <t>366882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>130531</t>
+          <t>139113</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103003</t>
+          <t>116551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157860</t>
+          <t>162778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>434676</t>
+          <t>472913</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376870</t>
+          <t>435351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>477562</t>
+          <t>515745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926199</t>
+          <t>989452</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926199</t>
+          <t>989452</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926199</t>
+          <t>989452</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1093673</t>
+          <t>1117796</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1093673</t>
+          <t>1117796</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1093673</t>
+          <t>1117796</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019871</t>
+          <t>2107249</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019871</t>
+          <t>2107249</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019871</t>
+          <t>2107249</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1616269</t>
+          <t>2251481</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2302431</t>
+          <t>2374350</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3353826</t>
+          <t>3345644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3455773</t>
+          <t>3421280</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4883769</t>
+          <t>5618246</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5758566</t>
+          <t>5775071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1338110</t>
+          <t>1219112</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1156287</t>
+          <t>1157319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1842449</t>
+          <t>1280188</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>313443</t>
+          <t>349786</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>255247</t>
+          <t>314429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357194</t>
+          <t>390065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1651553</t>
+          <t>1568897</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1411172</t>
+          <t>1492307</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2285969</t>
+          <t>1649132</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P3A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2007 (tasa de respuesta: 99,92%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2012 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2016 (tasa de respuesta: 99,8%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
